--- a/data/performance/daily/signal_list_2026-05-17.xlsx
+++ b/data/performance/daily/signal_list_2026-05-17.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 29.0%  (9W / 22L of 31 evaluated)</t>
+          <t>Win Rate: 35.5%  (11W / 20L of 31 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2290</v>
+        <v>2270</v>
       </c>
       <c r="D7" t="n">
         <v>2310</v>
@@ -637,10 +637,10 @@
         <v>2380</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.93</v>
+        <v>4.85</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.87</v>
+        <v>1.76</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="D9" t="n">
         <v>1600</v>
@@ -721,10 +721,10 @@
         <v>1630</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.84</v>
+        <v>-2.14</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="D11" t="n">
         <v>2380</v>
@@ -805,14 +805,14 @@
         <v>2390</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.84</v>
+        <v>0.42</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="D12" t="n">
         <v>1200</v>
@@ -847,10 +847,10 @@
         <v>1240</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.83</v>
+        <v>-2.44</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6025</v>
+        <v>6125</v>
       </c>
       <c r="D15" t="n">
         <v>5925</v>
@@ -973,10 +973,10 @@
         <v>6025</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.66</v>
+        <v>-3.27</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2750</v>
+        <v>2550</v>
       </c>
       <c r="D20" t="n">
         <v>2670</v>
@@ -1183,14 +1183,14 @@
         <v>2890</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.09</v>
+        <v>13.33</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.91</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.71</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6850</v>
+        <v>6875</v>
       </c>
       <c r="D22" t="n">
         <v>6575</v>
@@ -1267,10 +1267,10 @@
         <v>6900</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.73</v>
+        <v>0.36</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.01</v>
+        <v>-4.36</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>965</v>
+        <v>880</v>
       </c>
       <c r="D25" t="n">
         <v>945</v>
@@ -1393,14 +1393,14 @@
         <v>965</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>9.66</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>7.39</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D26" t="n">
         <v>240</v>
@@ -1435,10 +1435,10 @@
         <v>240</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>13.21</v>
+        <v>2.56</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>13.21</v>
+        <v>2.56</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D27" t="n">
         <v>224</v>
@@ -1477,10 +1477,10 @@
         <v>232</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.61</v>
+        <v>-3.45</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D29" t="n">
         <v>157</v>
@@ -1561,10 +1561,10 @@
         <v>165</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.48</v>
+        <v>3.12</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.48</v>
+        <v>-1.88</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="D30" t="n">
         <v>985</v>
@@ -1603,14 +1603,14 @@
         <v>1015</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.53</v>
+        <v>3.57</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.51</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D32" t="n">
         <v>80</v>
@@ -1687,10 +1687,10 @@
         <v>87</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>17.57</v>
+        <v>16</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.109999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2500</v>
+        <v>2520</v>
       </c>
       <c r="D35" t="n">
         <v>2460</v>
@@ -1813,10 +1813,10 @@
         <v>2510</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.6</v>
+        <v>-2.38</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
